--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty India Consumption ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty India Consumption ETF.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="115">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty India Consumption ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -94,21 +94,21 @@
     <t>INE030A01027</t>
   </si>
   <si>
+    <t>Zomato Ltd.</t>
+  </si>
+  <si>
+    <t>INE758T01015</t>
+  </si>
+  <si>
+    <t>Retailing</t>
+  </si>
+  <si>
     <t>Maruti Suzuki India Ltd.</t>
   </si>
   <si>
     <t>INE585B01010</t>
   </si>
   <si>
-    <t>Zomato Ltd.</t>
-  </si>
-  <si>
-    <t>INE758T01015</t>
-  </si>
-  <si>
-    <t>Retailing</t>
-  </si>
-  <si>
     <t>Titan Company Ltd.</t>
   </si>
   <si>
@@ -124,6 +124,15 @@
     <t>INE849A01020</t>
   </si>
   <si>
+    <t>Interglobe Aviation Ltd.</t>
+  </si>
+  <si>
+    <t>INE646L01027</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
+  </si>
+  <si>
     <t>Asian Paints Ltd.</t>
   </si>
   <si>
@@ -136,15 +145,6 @@
     <t>INE917I01010</t>
   </si>
   <si>
-    <t>Interglobe Aviation Ltd.</t>
-  </si>
-  <si>
-    <t>INE646L01027</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
     <t>Nestle India Ltd.</t>
   </si>
   <si>
@@ -163,6 +163,57 @@
     <t>Healthcare Services</t>
   </si>
   <si>
+    <t>Eicher Motors Ltd.</t>
+  </si>
+  <si>
+    <t>INE066A01021</t>
+  </si>
+  <si>
+    <t>Tata Consumer Products Ltd.</t>
+  </si>
+  <si>
+    <t>INE192A01025</t>
+  </si>
+  <si>
+    <t>Agricultural Food &amp; Other Products</t>
+  </si>
+  <si>
+    <t>Apollo Hospitals Enterprise Ltd.</t>
+  </si>
+  <si>
+    <t>INE437A01024</t>
+  </si>
+  <si>
+    <t>The Indian Hotels Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE053A01029</t>
+  </si>
+  <si>
+    <t>Leisure Services</t>
+  </si>
+  <si>
+    <t>Tata Power Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE245A01021</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>TVS Motor Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE494B01023</t>
+  </si>
+  <si>
+    <t>Britannia Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE216A01030</t>
+  </si>
+  <si>
     <t>Varun Beverages Ltd.</t>
   </si>
   <si>
@@ -172,73 +223,31 @@
     <t>Beverages</t>
   </si>
   <si>
-    <t>Eicher Motors Ltd.</t>
-  </si>
-  <si>
-    <t>INE066A01021</t>
-  </si>
-  <si>
-    <t>Apollo Hospitals Enterprise Ltd.</t>
-  </si>
-  <si>
-    <t>INE437A01024</t>
-  </si>
-  <si>
-    <t>The Indian Hotels Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE053A01029</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
-    <t>Tata Consumer Products Ltd.</t>
-  </si>
-  <si>
-    <t>INE192A01025</t>
-  </si>
-  <si>
-    <t>Agricultural Food &amp; Other Products</t>
-  </si>
-  <si>
-    <t>Tata Power Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE245A01021</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>Britannia Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE216A01030</t>
+    <t>Godrej Consumer Products Ltd.</t>
+  </si>
+  <si>
+    <t>INE102D01028</t>
+  </si>
+  <si>
+    <t>Personal Products</t>
+  </si>
+  <si>
+    <t>Avenue Supermarts Ltd.</t>
+  </si>
+  <si>
+    <t>INE192R01011</t>
+  </si>
+  <si>
+    <t>Hero Motocorp Ltd.</t>
+  </si>
+  <si>
+    <t>INE158A01026</t>
   </si>
   <si>
     <t>Info Edge (India) Ltd.</t>
   </si>
   <si>
-    <t>INE663F01024</t>
-  </si>
-  <si>
-    <t>TVS Motor Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE494B01023</t>
-  </si>
-  <si>
-    <t>Hero Motocorp Ltd.</t>
-  </si>
-  <si>
-    <t>INE158A01026</t>
-  </si>
-  <si>
-    <t>Avenue Supermarts Ltd.</t>
-  </si>
-  <si>
-    <t>INE192R01011</t>
+    <t>INE663F01032</t>
   </si>
   <si>
     <t>DLF Ltd.</t>
@@ -250,15 +259,6 @@
     <t>Realty</t>
   </si>
   <si>
-    <t>Godrej Consumer Products Ltd.</t>
-  </si>
-  <si>
-    <t>INE102D01028</t>
-  </si>
-  <si>
-    <t>Personal Products</t>
-  </si>
-  <si>
     <t>United Spirits Ltd.</t>
   </si>
   <si>
@@ -283,12 +283,6 @@
     <t>INE259A01022</t>
   </si>
   <si>
-    <t>ITC Hotels Ltd</t>
-  </si>
-  <si>
-    <t>INE379A01028</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -331,6 +325,9 @@
     <t>TREPS</t>
   </si>
   <si>
+    <t>^</t>
+  </si>
+  <si>
     <t>Net Current Assets</t>
   </si>
   <si>
@@ -340,13 +337,16 @@
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
+    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
+  </si>
+  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -1226,10 +1226,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>5803.2699999999995</v>
+        <v>6370.7699999999995</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9999757832213998</v>
+        <v>0.9978179022585999</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1263,10 +1263,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>5803.2699999999995</v>
+        <v>6370.7699999999995</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9999757832213998</v>
+        <v>0.9978179022585999</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1289,13 +1289,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>37053</v>
+        <v>34816</v>
       </c>
       <c r="G8" s="15">
-        <v>602.59</v>
+        <v>646.25</v>
       </c>
       <c r="H8" s="16">
-        <v>0.1038337708244</v>
+        <v>0.101218505665</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1318,13 +1318,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>124253</v>
+        <v>146980</v>
       </c>
       <c r="G9" s="15">
-        <v>556.03</v>
+        <v>614.45</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0958109022577</v>
+        <v>0.0962378503765</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1347,13 +1347,13 @@
         <v>23</v>
       </c>
       <c r="F10" s="14">
-        <v>16608</v>
+        <v>17934</v>
       </c>
       <c r="G10" s="15">
-        <v>496.55</v>
+        <v>533.86</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0855617565888</v>
+        <v>0.0836154915811</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1376,13 +1376,13 @@
         <v>20</v>
       </c>
       <c r="F11" s="14">
-        <v>16653</v>
+        <v>17963</v>
       </c>
       <c r="G11" s="15">
-        <v>411.13</v>
+        <v>421.83</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0708428254684</v>
+        <v>0.0660688622741</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1402,16 +1402,16 @@
         <v>13</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F12" s="14">
-        <v>2467</v>
+        <v>140638</v>
       </c>
       <c r="G12" s="15">
-        <v>303.70</v>
+        <v>335.15</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0523312969006</v>
+        <v>0.0524926610036</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1422,25 +1422,25 @@
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1">
       <c r="B13" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F13" s="14">
-        <v>130048</v>
+        <v>2654</v>
       </c>
       <c r="G13" s="15">
-        <v>286.56</v>
+        <v>326.95</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0493778611783</v>
+        <v>0.0512083410865</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1463,13 +1463,13 @@
         <v>33</v>
       </c>
       <c r="F14" s="14">
-        <v>7761</v>
+        <v>8346</v>
       </c>
       <c r="G14" s="15">
-        <v>270.88</v>
+        <v>296.70</v>
       </c>
       <c r="H14" s="16">
-        <v>0.046676001661</v>
+        <v>0.0464704535873</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1489,16 +1489,16 @@
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F15" s="14">
-        <v>4165</v>
+        <v>4497</v>
       </c>
       <c r="G15" s="15">
-        <v>239.62</v>
+        <v>253.79</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0412895138733</v>
+        <v>0.0397497014355</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1518,16 +1518,16 @@
         <v>13</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F16" s="14">
-        <v>8483</v>
+        <v>3969</v>
       </c>
       <c r="G16" s="15">
-        <v>195.18</v>
+        <v>211.55</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0336319477414</v>
+        <v>0.0331338876184</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1538,25 +1538,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F17" s="14">
-        <v>2081</v>
+        <v>9156</v>
       </c>
       <c r="G17" s="15">
-        <v>184.12</v>
+        <v>206.84</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0317261718319</v>
+        <v>0.032396186788</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1567,25 +1567,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="F18" s="14">
-        <v>3678</v>
+        <v>2244</v>
       </c>
       <c r="G18" s="15">
-        <v>159.05</v>
+        <v>193.14</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0274062982286</v>
+        <v>0.0302504327801</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1608,13 +1608,13 @@
         <v>45</v>
       </c>
       <c r="F19" s="14">
-        <v>6717</v>
+        <v>7255</v>
       </c>
       <c r="G19" s="15">
-        <v>155.38</v>
+        <v>173.84</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0267739114666</v>
+        <v>0.0272275822434</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1637,13 +1637,13 @@
         <v>48</v>
       </c>
       <c r="F20" s="14">
-        <v>13926</v>
+        <v>15051</v>
       </c>
       <c r="G20" s="15">
-        <v>147.79</v>
+        <v>169.35</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0254660598253</v>
+        <v>0.0265243387765</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1663,16 +1663,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F21" s="14">
-        <v>25132</v>
+        <v>2779</v>
       </c>
       <c r="G21" s="15">
-        <v>134.90</v>
+        <v>148.22</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0232449520971</v>
+        <v>0.0232148656242</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1683,25 +1683,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="D22" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>23</v>
-      </c>
       <c r="F22" s="14">
-        <v>2580</v>
+        <v>13189</v>
       </c>
       <c r="G22" s="15">
-        <v>134.01</v>
+        <v>145.91</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0230915939995</v>
+        <v>0.0228530633061</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1724,13 +1724,13 @@
         <v>48</v>
       </c>
       <c r="F23" s="14">
-        <v>1898</v>
+        <v>2042</v>
       </c>
       <c r="G23" s="15">
-        <v>129.26</v>
+        <v>140.50</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0222731097707</v>
+        <v>0.0220057254095</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1753,13 +1753,13 @@
         <v>58</v>
       </c>
       <c r="F24" s="14">
-        <v>16495</v>
+        <v>17788</v>
       </c>
       <c r="G24" s="15">
-        <v>126.14</v>
+        <v>136.94</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0217354948668</v>
+        <v>0.0214481426162</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1782,13 +1782,13 @@
         <v>61</v>
       </c>
       <c r="F25" s="14">
-        <v>12205</v>
+        <v>34005</v>
       </c>
       <c r="G25" s="15">
-        <v>125.06</v>
+        <v>133.57</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0215493974</v>
+        <v>0.0209203184552</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1808,16 +1808,16 @@
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="F26" s="14">
-        <v>31677</v>
+        <v>4753</v>
       </c>
       <c r="G26" s="15">
-        <v>115.46</v>
+        <v>132.17</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0198951976955</v>
+        <v>0.020701044323</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -1828,10 +1828,10 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>65</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>66</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>13</v>
@@ -1840,13 +1840,13 @@
         <v>45</v>
       </c>
       <c r="F27" s="14">
-        <v>2210</v>
+        <v>2386</v>
       </c>
       <c r="G27" s="15">
-        <v>113.37</v>
+        <v>131.48</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0195350646349</v>
+        <v>0.0205929735007</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -1857,25 +1857,25 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="D28" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>30</v>
-      </c>
       <c r="F28" s="14">
-        <v>1466</v>
+        <v>27165</v>
       </c>
       <c r="G28" s="15">
-        <v>113.23</v>
+        <v>129.29</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0195109408892</v>
+        <v>0.0202499661082</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -1895,16 +1895,16 @@
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="F29" s="14">
-        <v>4399</v>
+        <v>9702</v>
       </c>
       <c r="G29" s="15">
-        <v>108.12</v>
+        <v>119.47</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0186304241715</v>
+        <v>0.0187119146952</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -1915,25 +1915,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F30" s="14">
-        <v>2431</v>
+        <v>2977</v>
       </c>
       <c r="G30" s="15">
-        <v>105.48</v>
+        <v>119.14</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0181755192528</v>
+        <v>0.0186602286497</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -1944,25 +1944,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F31" s="14">
-        <v>2774</v>
+        <v>2627</v>
       </c>
       <c r="G31" s="15">
-        <v>101.66</v>
+        <v>113.21</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0175172856204</v>
+        <v>0.0177314460755</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -1973,25 +1973,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="F32" s="14">
-        <v>12026</v>
+        <v>7861</v>
       </c>
       <c r="G32" s="15">
-        <v>89.60</v>
+        <v>112.22</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0154391972416</v>
+        <v>0.0175763879392</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2014,13 +2014,13 @@
         <v>80</v>
       </c>
       <c r="F33" s="14">
-        <v>7065</v>
+        <v>12997</v>
       </c>
       <c r="G33" s="15">
-        <v>79.22</v>
+        <v>103.70</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0136505938112</v>
+        <v>0.0162419482204</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2040,16 +2040,16 @@
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F34" s="14">
-        <v>5537</v>
+        <v>5986</v>
       </c>
       <c r="G34" s="15">
-        <v>78.85</v>
+        <v>90.99</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0135868381976</v>
+        <v>0.0142512523488</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2069,16 +2069,16 @@
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F35" s="14">
-        <v>14752</v>
+        <v>15946</v>
       </c>
       <c r="G35" s="15">
-        <v>75.71</v>
+        <v>86.71</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0130457770442</v>
+        <v>0.0135809000018</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2101,13 +2101,13 @@
         <v>33</v>
       </c>
       <c r="F36" s="14">
-        <v>4747</v>
+        <v>5116</v>
       </c>
       <c r="G36" s="15">
-        <v>74.35</v>
+        <v>78.12</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0128114320861</v>
+        <v>0.0122354965764</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2127,16 +2127,16 @@
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F37" s="14">
-        <v>2482</v>
+        <v>2664</v>
       </c>
       <c r="G37" s="15">
-        <v>70.03</v>
+        <v>65.43</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0120670422191</v>
+        <v>0.0102479331925</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2147,35 +2147,35 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" ht="15" customHeight="1">
+      <c r="B39" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D38" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F38" s="14">
-        <v>12423</v>
-      </c>
-      <c r="G38" s="15">
-        <v>20.24</v>
-      </c>
-      <c r="H38" s="16">
-        <v>0.0034876043769</v>
-      </c>
-      <c r="I38" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J38" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" ht="15" customHeight="1">
-      <c r="B39" s="12" t="s">
+      <c r="H39" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I39" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J39" s="11" t="s">
@@ -2183,480 +2183,480 @@
       </c>
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" ht="15" customHeight="1">
+      <c r="B41" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="9" t="s">
+      <c r="C41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" ht="15" customHeight="1">
+      <c r="B42" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" ht="15" customHeight="1">
+      <c r="B43" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" ht="15" customHeight="1">
+      <c r="B44" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" ht="15" customHeight="1">
+      <c r="B45" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="H40" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J40" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" ht="15" customHeight="1">
-      <c r="B41" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J41" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" ht="15" customHeight="1">
-      <c r="B42" s="7" t="s">
+      <c r="C45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" ht="15" customHeight="1">
+      <c r="B46" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" ht="15" customHeight="1">
+      <c r="B47" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J42" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" ht="15" customHeight="1">
-      <c r="B43" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" ht="15" customHeight="1">
-      <c r="B44" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J44" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10" ht="15" customHeight="1">
-      <c r="B45" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" ht="15" customHeight="1">
-      <c r="B46" s="7" t="s">
+      <c r="C47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" ht="15" customHeight="1">
+      <c r="B48" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="15" customHeight="1">
+      <c r="B49" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C46" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J46" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" ht="15" customHeight="1">
-      <c r="B47" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J47" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" ht="15" customHeight="1">
-      <c r="B48" s="7" t="s">
+      <c r="C49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" ht="15" customHeight="1">
+      <c r="B50" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" ht="15" customHeight="1">
+      <c r="B51" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J48" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" ht="15" customHeight="1">
-      <c r="B49" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" ht="15" customHeight="1">
-      <c r="B50" s="7" t="s">
+      <c r="C51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" ht="15" customHeight="1">
+      <c r="B52" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" ht="15" customHeight="1">
+      <c r="B53" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" ht="15" customHeight="1">
-      <c r="B51" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" ht="15" customHeight="1">
-      <c r="B52" s="7" t="s">
+      <c r="C53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" ht="15" customHeight="1">
+      <c r="B54" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" ht="15" customHeight="1">
+      <c r="B55" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C52" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H52" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I52" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J52" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" ht="15" customHeight="1">
-      <c r="B53" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" ht="15" customHeight="1">
-      <c r="B54" s="7" t="s">
+      <c r="C55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" ht="15" customHeight="1">
+      <c r="B56" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" ht="15" customHeight="1">
+      <c r="B57" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H54" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J54" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10" ht="15" customHeight="1">
-      <c r="B55" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J55" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10" ht="15" customHeight="1">
-      <c r="B56" s="7" t="s">
+      <c r="C57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" ht="15" customHeight="1">
+      <c r="B58" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" ht="15" customHeight="1">
+      <c r="B59" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C56" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H56" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J56" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10" ht="15" customHeight="1">
-      <c r="B57" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J57" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10" ht="15" customHeight="1">
-      <c r="B58" s="7" t="s">
+      <c r="C59" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" ht="15" customHeight="1">
+      <c r="B60" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" ht="15" customHeight="1">
+      <c r="B61" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C58" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G58" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I58" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J58" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10" ht="15" customHeight="1">
-      <c r="B59" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J59" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10" ht="15" customHeight="1">
-      <c r="B60" s="7" t="s">
+      <c r="C61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" ht="15" customHeight="1">
+      <c r="B62" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" ht="15" customHeight="1">
+      <c r="B63" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C60" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H60" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I60" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J60" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10" ht="15" customHeight="1">
-      <c r="B61" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J61" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10" ht="15" customHeight="1">
-      <c r="B62" s="7" t="s">
+      <c r="C63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J63" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" ht="15" customHeight="1">
+      <c r="B64" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J64" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" ht="15" customHeight="1">
+      <c r="B65" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C62" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H62" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I62" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J62" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10" ht="15" customHeight="1">
-      <c r="B63" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J63" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10" ht="15" customHeight="1">
-      <c r="B64" s="7" t="s">
+      <c r="C65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="9">
+        <v>0.14</v>
+      </c>
+      <c r="H65" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C64" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H64" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I64" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J64" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" ht="15" customHeight="1">
-      <c r="B65" s="12" t="s">
+      <c r="I65" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J65" s="11" t="s">
@@ -2664,39 +2664,39 @@
       </c>
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
-      <c r="B66" s="7" t="s">
+      <c r="B66" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" ht="15" customHeight="1">
+      <c r="B67" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="C66" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D66" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="9">
-        <v>2.32</v>
-      </c>
-      <c r="H66" s="10">
-        <v>0.0003997649285</v>
-      </c>
-      <c r="I66" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J66" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" ht="15" customHeight="1">
-      <c r="B67" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J67" s="11" t="s">
+      <c r="C67" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="18">
+        <v>13.792043899999953</v>
+      </c>
+      <c r="H67" s="19">
+        <v>0.0021601703266915942</v>
+      </c>
+      <c r="I67" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="20" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2717,10 +2717,10 @@
         <v>13</v>
       </c>
       <c r="G68" s="18">
-        <v>-2.179460100000142</v>
+        <v>6384.7020439</v>
       </c>
       <c r="H68" s="19">
-        <v>-0.00037554815138714914</v>
+        <v>0.9999999999984914</v>
       </c>
       <c r="I68" s="18" t="s">
         <v>13</v>
@@ -2729,36 +2729,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="2:10" ht="15" customHeight="1">
-      <c r="B69" s="17" t="s">
+    <row r="71" spans="2:9" ht="15" customHeight="1">
+      <c r="B71" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="C69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G69" s="18">
-        <v>5803.4105399</v>
-      </c>
-      <c r="H69" s="19">
-        <v>0.9999999999985127</v>
-      </c>
-      <c r="I69" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J69" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="2:9" ht="15" customHeight="1">
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21"/>
+      <c r="I71" s="21"/>
+    </row>
+    <row r="72" spans="2:8" ht="15" customHeight="1">
       <c r="B72" s="13" t="s">
         <v>107</v>
       </c>
@@ -2768,7 +2751,6 @@
       <c r="F72" s="21"/>
       <c r="G72" s="21"/>
       <c r="H72" s="21"/>
-      <c r="I72" s="21"/>
     </row>
     <row r="73" spans="2:8" ht="15" customHeight="1">
       <c r="B73" s="13" t="s">
@@ -2830,15 +2812,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="B73:H73"/>
     <mergeCell ref="B74:H74"/>
     <mergeCell ref="B75:H75"/>
     <mergeCell ref="B76:H76"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B72:I72"/>
-    <mergeCell ref="B73:H73"/>
+    <mergeCell ref="B71:I71"/>
+    <mergeCell ref="B72:H72"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
